--- a/docs/rnaseq/RNA-seq_metadata_template.xlsx
+++ b/docs/rnaseq/RNA-seq_metadata_template.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -574,15 +574,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Strandedness</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Align_Pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -617,16 +622,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>92.5</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Sensitive isolate</t>
         </is>
@@ -661,16 +670,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>91.8</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Sensitive isolate</t>
         </is>
@@ -705,16 +718,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>78.2</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Low quality - below 85% threshold</t>
         </is>
@@ -749,16 +766,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Resistant isolate</t>
         </is>
@@ -793,16 +814,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Resistant isolate</t>
         </is>
@@ -837,16 +862,20 @@
           <t>Untreated</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>94</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Resistant isolate</t>
         </is>
